--- a/output/2026-09-28/enriched_analysis.xlsx
+++ b/output/2026-09-28/enriched_analysis.xlsx
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>3.274</v>
+        <v>3.279</v>
       </c>
       <c r="W2" t="n">
-        <v>2933</v>
+        <v>2928</v>
       </c>
       <c r="X2" t="n">
         <v>23</v>
@@ -1161,13 +1161,13 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>0.844</v>
+        <v>0.826</v>
       </c>
       <c r="W3" t="n">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="X3" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Y3" t="n">
         <v>22</v>
@@ -1393,10 +1393,10 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>0.928</v>
+        <v>0.952</v>
       </c>
       <c r="W4" t="n">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F5" t="n">
         <v>19</v>
@@ -1623,13 +1623,13 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>1.003</v>
+        <v>0.974</v>
       </c>
       <c r="W5" t="n">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="X5" t="n">
-        <v>8.51</v>
+        <v>8.73</v>
       </c>
       <c r="Y5" t="n">
         <v>17</v>
@@ -1858,10 +1858,10 @@
         <v>0.052</v>
       </c>
       <c r="W6" t="n">
-        <v>2561</v>
+        <v>2556</v>
       </c>
       <c r="X6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="Y6" t="n">
         <v>36</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>0.445</v>
+        <v>0.443</v>
       </c>
       <c r="W7" t="n">
-        <v>2736</v>
+        <v>2748</v>
       </c>
       <c r="X7" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="Y7" t="n">
         <v>8</v>
@@ -2319,13 +2319,13 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>0.121</v>
+        <v>0.12</v>
       </c>
       <c r="W8" t="n">
-        <v>2594</v>
+        <v>2624</v>
       </c>
       <c r="X8" t="n">
-        <v>22.7</v>
+        <v>23</v>
       </c>
       <c r="Y8" t="n">
         <v>-3</v>
@@ -2551,13 +2551,13 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.307</v>
       </c>
       <c r="W9" t="n">
-        <v>1021</v>
+        <v>999</v>
       </c>
       <c r="X9" t="n">
-        <v>10</v>
+        <v>9.82</v>
       </c>
       <c r="Y9" t="n">
         <v>7</v>
@@ -2783,13 +2783,13 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>0.048</v>
+        <v>0.05</v>
       </c>
       <c r="W10" t="n">
-        <v>1722</v>
+        <v>1637</v>
       </c>
       <c r="X10" t="n">
-        <v>23.2</v>
+        <v>22</v>
       </c>
       <c r="Y10" t="n">
         <v>55</v>
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>1.814</v>
+        <v>1.785</v>
       </c>
       <c r="W11" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="n">
@@ -3245,13 +3245,13 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>0.045</v>
+        <v>0.046</v>
       </c>
       <c r="W12" t="n">
-        <v>15959</v>
+        <v>15696</v>
       </c>
       <c r="X12" t="n">
-        <v>40.6</v>
+        <v>40</v>
       </c>
       <c r="Y12" t="n">
         <v>83</v>
@@ -3477,13 +3477,13 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>0.143</v>
+        <v>0.13</v>
       </c>
       <c r="W13" t="n">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="X13" t="n">
-        <v>32.6</v>
+        <v>35.9</v>
       </c>
       <c r="Y13" t="n">
         <v>19</v>
@@ -3709,13 +3709,13 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>2.29</v>
+        <v>2.324</v>
       </c>
       <c r="W14" t="n">
-        <v>2563</v>
+        <v>2526</v>
       </c>
       <c r="X14" t="n">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="Y14" t="n">
         <v>6</v>
@@ -3869,12 +3869,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STEL</t>
+          <t>CHEMBOND</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>STEL HOLDINGS LIMITED</t>
+          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -3886,40 +3886,40 @@
         </is>
       </c>
       <c r="E15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" t="n">
         <v>12</v>
       </c>
-      <c r="F15" t="n">
-        <v>13</v>
-      </c>
       <c r="G15" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H15" t="n">
         <v>-1</v>
       </c>
       <c r="I15" t="n">
-        <v>619.3</v>
+        <v>191.99</v>
       </c>
       <c r="J15" t="n">
-        <v>636.71</v>
+        <v>170.45</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.7</v>
+        <v>12.6</v>
       </c>
       <c r="L15" t="n">
-        <v>64.68000000000001</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>4.12</v>
+        <v>0.26</v>
       </c>
       <c r="N15" t="n">
-        <v>41238002</v>
+        <v>2560187</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>41238002</v>
+        <v>2560187</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -3933,64 +3933,64 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>0.361</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="n">
-        <v>1143</v>
+        <v>256</v>
       </c>
       <c r="X15" t="n">
-        <v>58.2</v>
+        <v>27.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.11</v>
+        <v>1.87</v>
       </c>
       <c r="AA15" t="n">
-        <v>23</v>
+        <v>-31</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>3.36</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.58</v>
+        <v>4.96</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF15" t="n">
-        <v>-110</v>
+        <v>2.97</v>
       </c>
       <c r="AG15" t="n">
-        <v>590.22</v>
+        <v>181.14</v>
       </c>
       <c r="AH15" t="n">
-        <v>518.25</v>
+        <v>163.73</v>
       </c>
       <c r="AI15" t="n">
-        <v>45.3</v>
+        <v>57.4</v>
       </c>
       <c r="AJ15" t="n">
-        <v>636.7131718313339</v>
+        <v>170.4518641810919</v>
       </c>
       <c r="AK15" t="n">
-        <v>-2.7</v>
+        <v>12.6</v>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4000,57 +4000,57 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="AQ15" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="AS15" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="AT15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="AW15" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="AX15" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="AY15" t="n">
-        <v>2255167</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>16560542</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>21276462</v>
+        <v>2560187</v>
       </c>
       <c r="BB15" t="n">
-        <v>38328962</v>
+        <v>2560187</v>
       </c>
       <c r="BC15" t="n">
-        <v>38328962</v>
+        <v>2560187</v>
       </c>
       <c r="BD15" t="n">
         <v>0</v>
@@ -4083,10 +4083,10 @@
         <v>0</v>
       </c>
       <c r="BN15" t="n">
-        <v>2255167</v>
+        <v>0</v>
       </c>
       <c r="BO15" t="n">
-        <v>21276462</v>
+        <v>2560187</v>
       </c>
       <c r="BP15" t="n">
         <v>2</v>
@@ -4095,22 +4095,22 @@
         <v>0</v>
       </c>
       <c r="BR15" t="n">
-        <v>0.106</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ASAHISONG</t>
+          <t>STEL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ASAHI SONGWON COLORS LIMITED</t>
+          <t>STEL HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4118,171 +4118,171 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F16" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G16" t="n">
+        <v>17</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>619.3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>636.71</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="L16" t="n">
+        <v>64.68000000000001</v>
+      </c>
+      <c r="M16" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="N16" t="n">
+        <v>41238002</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>41238002</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>34</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>24-09-2026</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1160</v>
+      </c>
+      <c r="X16" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="Y16" t="n">
         <v>21</v>
       </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>402.75</v>
-      </c>
-      <c r="J16" t="n">
-        <v>338.1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>66.73</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3381000</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>3381000</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S16" t="b">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>11-08-2026</t>
-        </is>
-      </c>
-      <c r="V16" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="W16" t="n">
-        <v>475</v>
-      </c>
-      <c r="X16" t="n">
+      <c r="Z16" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-110</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>590.22</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>518.25</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>636.7131718313339</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>24-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ16" t="n">
+        <v>91</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>95</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV16" t="n">
         <v>14</v>
       </c>
-      <c r="Y16" t="n">
-        <v>-8</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA16" t="n">
+      <c r="AW16" t="n">
         <v>33</v>
       </c>
-      <c r="AB16" t="n">
-        <v>14.36</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>9.94</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>359.64</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>270.07</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>101.1</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>338.1</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>Aging</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Mature Accumulation</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>Mature — Wait for Pullback</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>11-08-2026</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>11-08-2026</t>
-        </is>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>48</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>48</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1</v>
-      </c>
       <c r="AX16" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>2255167</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>16560542</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>21276462</v>
       </c>
       <c r="BB16" t="n">
-        <v>3381000</v>
+        <v>38328962</v>
       </c>
       <c r="BC16" t="n">
-        <v>3381000</v>
+        <v>38328962</v>
       </c>
       <c r="BD16" t="n">
         <v>0</v>
@@ -4315,45 +4315,45 @@
         <v>0</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>2255167</v>
       </c>
       <c r="BO16" t="n">
-        <v>0</v>
+        <v>21276462</v>
       </c>
       <c r="BP16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ16" t="n">
         <v>0</v>
       </c>
       <c r="BR16" t="n">
-        <v>0</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>JAYAGROGN</t>
+          <t>ASAHISONG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jayant Agro-Organics Limited</t>
+          <t>ASAHI SONGWON COLORS LIMITED</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Fundamental Watch</t>
+          <t>Watchlist</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G17" t="n">
         <v>21</v>
@@ -4362,28 +4362,28 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>234.84</v>
+        <v>402.75</v>
       </c>
       <c r="J17" t="n">
-        <v>234.4</v>
+        <v>338.1</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2</v>
+        <v>19.1</v>
       </c>
       <c r="L17" t="n">
-        <v>67.13</v>
+        <v>66.73</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
       <c r="N17" t="n">
-        <v>2995877</v>
+        <v>3381000</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2995877</v>
+        <v>3381000</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -4397,124 +4397,124 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="V17" t="n">
-        <v>0.042</v>
+        <v>0.073</v>
       </c>
       <c r="W17" t="n">
-        <v>705</v>
+        <v>461</v>
       </c>
       <c r="X17" t="n">
-        <v>11.5</v>
+        <v>13.6</v>
       </c>
       <c r="Y17" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="Z17" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AA17" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.54</v>
+        <v>14.36</v>
       </c>
       <c r="AC17" t="n">
-        <v>14.8</v>
+        <v>9.94</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.11</v>
+        <v>0.23</v>
       </c>
       <c r="AE17" t="b">
         <v>1</v>
       </c>
       <c r="AF17" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AG17" t="n">
-        <v>227.7</v>
+        <v>359.64</v>
       </c>
       <c r="AH17" t="n">
-        <v>205.16</v>
+        <v>270.07</v>
       </c>
       <c r="AI17" t="n">
-        <v>40.7</v>
+        <v>101.1</v>
       </c>
       <c r="AJ17" t="n">
-        <v>234.4008293560754</v>
+        <v>338.1</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.2</v>
+        <v>19.1</v>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="AQ17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="AS17" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="AT17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AX17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY17" t="n">
-        <v>1358248</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>2995877</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>2995877</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>2995877</v>
+        <v>3381000</v>
       </c>
       <c r="BC17" t="n">
-        <v>2995877</v>
+        <v>3381000</v>
       </c>
       <c r="BD17" t="n">
         <v>0</v>
@@ -4547,10 +4547,10 @@
         <v>0</v>
       </c>
       <c r="BN17" t="n">
-        <v>1358248</v>
+        <v>0</v>
       </c>
       <c r="BO17" t="n">
-        <v>2995877</v>
+        <v>0</v>
       </c>
       <c r="BP17" t="n">
         <v>1</v>
@@ -4559,18 +4559,18 @@
         <v>0</v>
       </c>
       <c r="BR17" t="n">
-        <v>0.4534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CHEMBOND</t>
+          <t>JAYAGROGN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
+          <t>Jayant Agro-Organics Limited</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -4582,40 +4582,40 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F18" t="n">
         <v>12</v>
       </c>
       <c r="G18" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H18" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>191.99</v>
+        <v>234.84</v>
       </c>
       <c r="J18" t="n">
-        <v>170.45</v>
+        <v>234.4</v>
       </c>
       <c r="K18" t="n">
-        <v>12.6</v>
+        <v>0.2</v>
       </c>
       <c r="L18" t="n">
-        <v>67.54000000000001</v>
+        <v>67.13</v>
       </c>
       <c r="M18" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="N18" t="n">
-        <v>2560187</v>
+        <v>2995877</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2560187</v>
+        <v>2995877</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -4629,124 +4629,124 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
       <c r="V18" t="n">
-        <v>0.099</v>
+        <v>0.043</v>
       </c>
       <c r="W18" t="n">
-        <v>258</v>
+        <v>689</v>
       </c>
       <c r="X18" t="n">
-        <v>27.6</v>
+        <v>11.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>24</v>
+        <v>-5</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.87</v>
+        <v>32</v>
       </c>
       <c r="AA18" t="n">
-        <v>-31</v>
+        <v>1</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.36</v>
+        <v>6.54</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.96</v>
+        <v>14.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AE18" t="b">
         <v>1</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.97</v>
+        <v>9</v>
       </c>
       <c r="AG18" t="n">
-        <v>181.14</v>
+        <v>227.7</v>
       </c>
       <c r="AH18" t="n">
-        <v>163.73</v>
+        <v>205.16</v>
       </c>
       <c r="AI18" t="n">
-        <v>57.4</v>
+        <v>40.7</v>
       </c>
       <c r="AJ18" t="n">
-        <v>170.4518641810919</v>
+        <v>234.4008293560754</v>
       </c>
       <c r="AK18" t="n">
-        <v>12.6</v>
+        <v>0.2</v>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR18" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="AS18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1358248</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>2995877</v>
       </c>
       <c r="BA18" t="n">
-        <v>2560187</v>
+        <v>2995877</v>
       </c>
       <c r="BB18" t="n">
-        <v>2560187</v>
+        <v>2995877</v>
       </c>
       <c r="BC18" t="n">
-        <v>2560187</v>
+        <v>2995877</v>
       </c>
       <c r="BD18" t="n">
         <v>0</v>
@@ -4779,19 +4779,19 @@
         <v>0</v>
       </c>
       <c r="BN18" t="n">
-        <v>0</v>
+        <v>1358248</v>
       </c>
       <c r="BO18" t="n">
-        <v>2560187</v>
+        <v>2995877</v>
       </c>
       <c r="BP18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ18" t="n">
         <v>0</v>
       </c>
       <c r="BR18" t="n">
-        <v>0</v>
+        <v>0.4534</v>
       </c>
     </row>
     <row r="19">
@@ -4869,13 +4869,13 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>2.86</v>
+        <v>2.844</v>
       </c>
       <c r="W19" t="n">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="X19" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="Y19" t="n">
         <v>30</v>
@@ -5095,13 +5095,13 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>0.624</v>
+        <v>0.633</v>
       </c>
       <c r="W20" t="n">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="X20" t="n">
-        <v>1214</v>
+        <v>1196</v>
       </c>
       <c r="Y20" t="n">
         <v>-61</v>
@@ -5323,13 +5323,13 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>0.265</v>
+        <v>0.267</v>
       </c>
       <c r="W21" t="n">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="X21" t="n">
-        <v>39.1</v>
+        <v>38.7</v>
       </c>
       <c r="Y21" t="n">
         <v>-44</v>
@@ -5555,13 +5555,13 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>0.493</v>
+        <v>0.497</v>
       </c>
       <c r="W22" t="n">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="X22" t="n">
-        <v>37.6</v>
+        <v>37.3</v>
       </c>
       <c r="Y22" t="n">
         <v>21</v>
@@ -5790,10 +5790,10 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="X23" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="Y23" t="n">
         <v>19</v>
@@ -6017,10 +6017,10 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
       <c r="W24" t="n">
-        <v>999</v>
+        <v>1010</v>
       </c>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="n">
@@ -6250,10 +6250,10 @@
         <v>0.162</v>
       </c>
       <c r="W25" t="n">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="X25" t="n">
-        <v>57.3</v>
+        <v>57.2</v>
       </c>
       <c r="Y25" t="n">
         <v>3</v>
@@ -6271,7 +6271,7 @@
         <v>11.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE25" t="b">
         <v>1</v>
@@ -6479,13 +6479,13 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>0.059</v>
+        <v>0.057</v>
       </c>
       <c r="W26" t="n">
-        <v>1874</v>
+        <v>1916</v>
       </c>
       <c r="X26" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Y26" t="n">
         <v>20</v>
@@ -6714,10 +6714,10 @@
         <v>0.05</v>
       </c>
       <c r="W27" t="n">
-        <v>5246</v>
+        <v>5231</v>
       </c>
       <c r="X27" t="n">
-        <v>34.2</v>
+        <v>34.1</v>
       </c>
       <c r="Y27" t="n">
         <v>-25</v>
@@ -6943,13 +6943,13 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>0.135</v>
+        <v>0.132</v>
       </c>
       <c r="W28" t="n">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="X28" t="n">
-        <v>5.93</v>
+        <v>6.1</v>
       </c>
       <c r="Y28" t="n">
         <v>118</v>
@@ -7171,13 +7171,13 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>0.858</v>
+        <v>0.866</v>
       </c>
       <c r="W29" t="n">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="X29" t="n">
-        <v>6.75</v>
+        <v>6.7</v>
       </c>
       <c r="Y29" t="n">
         <v>31</v>
@@ -7399,13 +7399,13 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>0.641</v>
+        <v>0.644</v>
       </c>
       <c r="W30" t="n">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="X30" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="Y30" t="n">
         <v>19</v>
@@ -7631,13 +7631,13 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>0.038</v>
+        <v>0.039</v>
       </c>
       <c r="W31" t="n">
-        <v>3490</v>
+        <v>3423</v>
       </c>
       <c r="X31" t="n">
-        <v>20.7</v>
+        <v>20.3</v>
       </c>
       <c r="Y31" t="n">
         <v>-4</v>
@@ -7866,10 +7866,10 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="W32" t="n">
-        <v>53444</v>
+        <v>53455</v>
       </c>
       <c r="X32" t="n">
-        <v>45.3</v>
+        <v>45.2</v>
       </c>
       <c r="Y32" t="n">
         <v>5</v>
@@ -8095,13 +8095,13 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>0.308</v>
+        <v>0.315</v>
       </c>
       <c r="W33" t="n">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="X33" t="n">
-        <v>24.3</v>
+        <v>23.8</v>
       </c>
       <c r="Y33" t="n">
         <v>12</v>
@@ -8330,10 +8330,10 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>3748</v>
+        <v>3527</v>
       </c>
       <c r="X34" t="n">
-        <v>84.40000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="Y34" t="n">
         <v>42</v>
@@ -8559,13 +8559,13 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="W35" t="n">
-        <v>9589</v>
+        <v>9522</v>
       </c>
       <c r="X35" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="Y35" t="n">
         <v>-12</v>
@@ -9020,10 +9020,10 @@
         <v>0.008</v>
       </c>
       <c r="W37" t="n">
-        <v>5427</v>
+        <v>5218</v>
       </c>
       <c r="X37" t="n">
-        <v>9.17</v>
+        <v>8.82</v>
       </c>
       <c r="Y37" t="n">
         <v>43</v>
@@ -9252,7 +9252,7 @@
         <v>0.217</v>
       </c>
       <c r="W38" t="n">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="X38" t="n">
         <v>14.2</v>
@@ -9481,13 +9481,13 @@
         </is>
       </c>
       <c r="V39" t="n">
-        <v>0.208</v>
+        <v>0.211</v>
       </c>
       <c r="W39" t="n">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="X39" t="n">
-        <v>25.7</v>
+        <v>25.3</v>
       </c>
       <c r="Y39" t="n">
         <v>21</v>
@@ -9713,13 +9713,13 @@
         </is>
       </c>
       <c r="V40" t="n">
-        <v>0.212</v>
+        <v>0.214</v>
       </c>
       <c r="W40" t="n">
-        <v>966</v>
+        <v>957</v>
       </c>
       <c r="X40" t="n">
-        <v>26.3</v>
+        <v>26.1</v>
       </c>
       <c r="Y40" t="n">
         <v>9</v>
@@ -10180,10 +10180,10 @@
         <v>0.074</v>
       </c>
       <c r="W42" t="n">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="X42" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="Y42" t="n">
         <v>185</v>
@@ -10410,7 +10410,7 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>8983</v>
+        <v>8932</v>
       </c>
       <c r="X43" t="n">
         <v>15.2</v>
@@ -10639,13 +10639,13 @@
         </is>
       </c>
       <c r="V44" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.674</v>
       </c>
       <c r="W44" t="n">
-        <v>3789</v>
+        <v>3864</v>
       </c>
       <c r="X44" t="n">
-        <v>26.5</v>
+        <v>27</v>
       </c>
       <c r="Y44" t="n">
         <v>2</v>
@@ -10871,13 +10871,13 @@
         </is>
       </c>
       <c r="V45" t="n">
-        <v>0.224</v>
+        <v>0.227</v>
       </c>
       <c r="W45" t="n">
-        <v>1785</v>
+        <v>1758</v>
       </c>
       <c r="X45" t="n">
-        <v>18.9</v>
+        <v>18.6</v>
       </c>
       <c r="Y45" t="n">
         <v>-3</v>
@@ -11106,10 +11106,10 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>118820</v>
+        <v>117300</v>
       </c>
       <c r="X46" t="n">
-        <v>34.2</v>
+        <v>33.8</v>
       </c>
       <c r="Y46" t="n">
         <v>18</v>
@@ -11335,13 +11335,13 @@
         </is>
       </c>
       <c r="V47" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="W47" t="n">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="X47" t="n">
-        <v>97.2</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="Y47" t="n">
         <v>246</v>
@@ -11567,13 +11567,13 @@
         </is>
       </c>
       <c r="V48" t="n">
-        <v>0.043</v>
+        <v>0.044</v>
       </c>
       <c r="W48" t="n">
-        <v>1613</v>
+        <v>1589</v>
       </c>
       <c r="X48" t="n">
-        <v>21.1</v>
+        <v>20.8</v>
       </c>
       <c r="Y48" t="n">
         <v>10</v>
@@ -11802,10 +11802,10 @@
         <v>0.082</v>
       </c>
       <c r="W49" t="n">
-        <v>1671</v>
+        <v>1659</v>
       </c>
       <c r="X49" t="n">
-        <v>30.2</v>
+        <v>30</v>
       </c>
       <c r="Y49" t="n">
         <v>39</v>
@@ -12486,140 +12486,140 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STEL</t>
+          <t>CHEMBOND</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>STEL HOLDINGS LIMITED</t>
+          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>619.3</v>
+        <v>191.99</v>
       </c>
       <c r="D15" t="n">
-        <v>636.71</v>
+        <v>170.45</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.7</v>
+        <v>12.6</v>
       </c>
       <c r="F15" t="n">
-        <v>64.68000000000001</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>4.12</v>
+        <v>0.26</v>
       </c>
       <c r="H15" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ASAHISONG</t>
+          <t>STEL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ASAHI SONGWON COLORS LIMITED</t>
+          <t>STEL HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>402.75</v>
+        <v>619.3</v>
       </c>
       <c r="D16" t="n">
-        <v>338.1</v>
+        <v>636.71</v>
       </c>
       <c r="E16" t="n">
-        <v>19.1</v>
+        <v>-2.7</v>
       </c>
       <c r="F16" t="n">
-        <v>66.73</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.34</v>
+        <v>4.12</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>JAYAGROGN</t>
+          <t>ASAHISONG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jayant Agro-Organics Limited</t>
+          <t>ASAHI SONGWON COLORS LIMITED</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>234.84</v>
+        <v>402.75</v>
       </c>
       <c r="D17" t="n">
-        <v>234.4</v>
+        <v>338.1</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2</v>
+        <v>19.1</v>
       </c>
       <c r="F17" t="n">
-        <v>67.13</v>
+        <v>66.73</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CHEMBOND</t>
+          <t>JAYAGROGN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
+          <t>Jayant Agro-Organics Limited</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>191.99</v>
+        <v>234.84</v>
       </c>
       <c r="D18" t="n">
-        <v>170.45</v>
+        <v>234.4</v>
       </c>
       <c r="E18" t="n">
-        <v>12.6</v>
+        <v>0.2</v>
       </c>
       <c r="F18" t="n">
-        <v>67.54000000000001</v>
+        <v>67.13</v>
       </c>
       <c r="G18" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
     </row>
@@ -13811,7 +13811,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -13831,7 +13831,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/output/2026-09-28/enriched_analysis.xlsx
+++ b/output/2026-09-28/enriched_analysis.xlsx
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>3.279</v>
+        <v>3.326</v>
       </c>
       <c r="W2" t="n">
-        <v>2928</v>
+        <v>2887</v>
       </c>
       <c r="X2" t="n">
-        <v>23</v>
+        <v>22.6</v>
       </c>
       <c r="Y2" t="n">
         <v>75</v>
@@ -1121,25 +1121,25 @@
         <v>351.5</v>
       </c>
       <c r="J3" t="n">
-        <v>324.91</v>
+        <v>326.23</v>
       </c>
       <c r="K3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="L3" t="n">
         <v>63.24</v>
       </c>
       <c r="M3" t="n">
-        <v>2.83</v>
+        <v>3.02</v>
       </c>
       <c r="N3" t="n">
-        <v>28263611</v>
+        <v>30209592</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>28263611</v>
+        <v>30209592</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1153,21 +1153,21 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>25-09-2026</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>0.826</v>
+        <v>0.886</v>
       </c>
       <c r="W3" t="n">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="X3" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Y3" t="n">
         <v>22</v>
@@ -1203,10 +1203,10 @@
         <v>58</v>
       </c>
       <c r="AJ3" t="n">
-        <v>324.9101725505524</v>
+        <v>326.2269256935521</v>
       </c>
       <c r="AK3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
@@ -1230,47 +1230,47 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>25-09-2026</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AR3" t="n">
         <v>66</v>
       </c>
       <c r="AS3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT3" t="n">
         <v>4</v>
       </c>
-      <c r="AT3" t="n">
-        <v>3</v>
-      </c>
       <c r="AU3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY3" t="n">
-        <v>1062257</v>
+        <v>3008238</v>
       </c>
       <c r="AZ3" t="n">
-        <v>10180123</v>
+        <v>12126104</v>
       </c>
       <c r="BA3" t="n">
-        <v>10885723</v>
+        <v>12831704</v>
       </c>
       <c r="BB3" t="n">
-        <v>15008863</v>
+        <v>16954844</v>
       </c>
       <c r="BC3" t="n">
-        <v>28263611</v>
+        <v>30209592</v>
       </c>
       <c r="BD3" t="n">
         <v>0</v>
@@ -1303,10 +1303,10 @@
         <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>1062257</v>
+        <v>3008238</v>
       </c>
       <c r="BO3" t="n">
-        <v>10885723</v>
+        <v>12831704</v>
       </c>
       <c r="BP3" t="n">
         <v>3</v>
@@ -1315,7 +1315,7 @@
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.2344</v>
       </c>
     </row>
     <row r="4">
@@ -1858,10 +1858,10 @@
         <v>0.052</v>
       </c>
       <c r="W6" t="n">
-        <v>2556</v>
+        <v>2547</v>
       </c>
       <c r="X6" t="n">
-        <v>8.779999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="Y6" t="n">
         <v>36</v>
@@ -2015,12 +2015,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ALEMBICLTD</t>
+          <t>INDORAMA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alembic Limited</t>
+          <t>INDO RAMA SYNTHETICS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G7" t="n">
         <v>25</v>
@@ -2044,28 +2044,28 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>106.53</v>
+        <v>99.36</v>
       </c>
       <c r="J7" t="n">
-        <v>95.19</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>11.9</v>
+        <v>31.3</v>
       </c>
       <c r="L7" t="n">
-        <v>70.88</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>12.18</v>
+        <v>3.14</v>
       </c>
       <c r="N7" t="n">
-        <v>121849300</v>
+        <v>31393588</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>121849300</v>
+        <v>31393588</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -2079,64 +2079,64 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>0.443</v>
+        <v>0.12</v>
       </c>
       <c r="W7" t="n">
-        <v>2748</v>
+        <v>2608</v>
       </c>
       <c r="X7" t="n">
-        <v>22.5</v>
+        <v>22.8</v>
       </c>
       <c r="Y7" t="n">
-        <v>8</v>
+        <v>-3</v>
       </c>
       <c r="Z7" t="n">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="AA7" t="n">
-        <v>-14</v>
+        <v>77</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.57</v>
+        <v>1.29</v>
       </c>
       <c r="AC7" t="n">
-        <v>16.9</v>
+        <v>15.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.01</v>
+        <v>1.69</v>
       </c>
       <c r="AE7" t="b">
         <v>1</v>
       </c>
       <c r="AF7" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="AG7" t="n">
-        <v>95.55</v>
+        <v>67.28</v>
       </c>
       <c r="AH7" t="n">
-        <v>92.44</v>
+        <v>47.67</v>
       </c>
       <c r="AI7" t="n">
-        <v>41.4</v>
+        <v>215.2</v>
       </c>
       <c r="AJ7" t="n">
-        <v>95.19335259867236</v>
+        <v>75.6844038997483</v>
       </c>
       <c r="AK7" t="n">
-        <v>11.9</v>
+        <v>31.3</v>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2146,57 +2146,57 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>08-09-2026</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="AR7" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="AS7" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
         <v>2</v>
       </c>
-      <c r="AU7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>5</v>
-      </c>
       <c r="AW7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AX7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AY7" t="n">
-        <v>24784680</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>36964024</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>59380273</v>
+        <v>31393588</v>
       </c>
       <c r="BB7" t="n">
-        <v>121849300</v>
+        <v>31393588</v>
       </c>
       <c r="BC7" t="n">
-        <v>121849300</v>
+        <v>31393588</v>
       </c>
       <c r="BD7" t="n">
         <v>0</v>
@@ -2229,10 +2229,10 @@
         <v>0</v>
       </c>
       <c r="BN7" t="n">
-        <v>24784680</v>
+        <v>0</v>
       </c>
       <c r="BO7" t="n">
-        <v>59380273</v>
+        <v>31393588</v>
       </c>
       <c r="BP7" t="n">
         <v>1</v>
@@ -2241,18 +2241,18 @@
         <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.4174</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>INDORAMA</t>
+          <t>ALEMBICLTD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>INDO RAMA SYNTHETICS (INDIA) LIMITED</t>
+          <t>Alembic Limited</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F8" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G8" t="n">
         <v>25</v>
@@ -2276,28 +2276,28 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>99.36</v>
+        <v>106.53</v>
       </c>
       <c r="J8" t="n">
-        <v>75.68000000000001</v>
+        <v>95.19</v>
       </c>
       <c r="K8" t="n">
-        <v>31.3</v>
+        <v>11.9</v>
       </c>
       <c r="L8" t="n">
-        <v>74.84999999999999</v>
+        <v>70.88</v>
       </c>
       <c r="M8" t="n">
-        <v>3.14</v>
+        <v>12.18</v>
       </c>
       <c r="N8" t="n">
-        <v>31393588</v>
+        <v>121849300</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>31393588</v>
+        <v>121849300</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2311,124 +2311,124 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>0.12</v>
+        <v>0.441</v>
       </c>
       <c r="W8" t="n">
-        <v>2624</v>
+        <v>2762</v>
       </c>
       <c r="X8" t="n">
-        <v>23</v>
+        <v>22.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>-3</v>
+        <v>8</v>
       </c>
       <c r="Z8" t="n">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="AA8" t="n">
-        <v>77</v>
+        <v>-14</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.29</v>
+        <v>0.57</v>
       </c>
       <c r="AC8" t="n">
-        <v>15.8</v>
+        <v>16.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.69</v>
+        <v>0.01</v>
       </c>
       <c r="AE8" t="b">
         <v>1</v>
       </c>
       <c r="AF8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>95.55</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>92.44</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>95.19335259867236</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>Mature — Wait for Pullback</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>17-08-2026</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>24-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW8" t="n">
         <v>8</v>
       </c>
-      <c r="AG8" t="n">
-        <v>67.28</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>47.67</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>215.2</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>75.6844038997483</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>Late — Poor Entry</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>08-09-2026</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>09-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>19</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>2</v>
-      </c>
       <c r="AX8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>24784680</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>36964024</v>
       </c>
       <c r="BA8" t="n">
-        <v>31393588</v>
+        <v>59380273</v>
       </c>
       <c r="BB8" t="n">
-        <v>31393588</v>
+        <v>121849300</v>
       </c>
       <c r="BC8" t="n">
-        <v>31393588</v>
+        <v>121849300</v>
       </c>
       <c r="BD8" t="n">
         <v>0</v>
@@ -2461,10 +2461,10 @@
         <v>0</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>24784680</v>
       </c>
       <c r="BO8" t="n">
-        <v>31393588</v>
+        <v>59380273</v>
       </c>
       <c r="BP8" t="n">
         <v>1</v>
@@ -2473,7 +2473,7 @@
         <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>0</v>
+        <v>0.4174</v>
       </c>
     </row>
     <row r="9">
@@ -2551,13 +2551,13 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>0.307</v>
+        <v>0.309</v>
       </c>
       <c r="W9" t="n">
-        <v>999</v>
+        <v>992</v>
       </c>
       <c r="X9" t="n">
-        <v>9.82</v>
+        <v>9.76</v>
       </c>
       <c r="Y9" t="n">
         <v>7</v>
@@ -2783,13 +2783,13 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>0.05</v>
+        <v>0.049</v>
       </c>
       <c r="W10" t="n">
-        <v>1637</v>
+        <v>1673</v>
       </c>
       <c r="X10" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="Y10" t="n">
         <v>55</v>
@@ -3248,10 +3248,10 @@
         <v>0.046</v>
       </c>
       <c r="W12" t="n">
-        <v>15696</v>
+        <v>15650</v>
       </c>
       <c r="X12" t="n">
-        <v>40</v>
+        <v>39.8</v>
       </c>
       <c r="Y12" t="n">
         <v>83</v>
@@ -3709,13 +3709,13 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>2.324</v>
+        <v>2.317</v>
       </c>
       <c r="W14" t="n">
-        <v>2526</v>
+        <v>2533</v>
       </c>
       <c r="X14" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Y14" t="n">
         <v>6</v>
@@ -3869,12 +3869,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CHEMBOND</t>
+          <t>STEL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
+          <t>STEL HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -3886,40 +3886,40 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G15" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H15" t="n">
         <v>-1</v>
       </c>
       <c r="I15" t="n">
-        <v>191.99</v>
+        <v>619.3</v>
       </c>
       <c r="J15" t="n">
-        <v>170.45</v>
+        <v>636.71</v>
       </c>
       <c r="K15" t="n">
-        <v>12.6</v>
+        <v>-2.7</v>
       </c>
       <c r="L15" t="n">
-        <v>67.54000000000001</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>0.26</v>
+        <v>4.12</v>
       </c>
       <c r="N15" t="n">
-        <v>2560187</v>
+        <v>41238002</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2560187</v>
+        <v>41238002</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -3933,64 +3933,64 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.364</v>
       </c>
       <c r="W15" t="n">
-        <v>256</v>
+        <v>1134</v>
       </c>
       <c r="X15" t="n">
-        <v>27.4</v>
+        <v>57.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.87</v>
+        <v>-0.11</v>
       </c>
       <c r="AA15" t="n">
-        <v>-31</v>
+        <v>23</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.36</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.96</v>
+        <v>1.58</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.97</v>
+        <v>-110</v>
       </c>
       <c r="AG15" t="n">
-        <v>181.14</v>
+        <v>590.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>163.73</v>
+        <v>518.25</v>
       </c>
       <c r="AI15" t="n">
-        <v>57.4</v>
+        <v>45.3</v>
       </c>
       <c r="AJ15" t="n">
-        <v>170.4518641810919</v>
+        <v>636.7131718313339</v>
       </c>
       <c r="AK15" t="n">
-        <v>12.6</v>
+        <v>-2.7</v>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4000,57 +4000,57 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="AR15" t="n">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="AS15" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AV15" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="AW15" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="AX15" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>2255167</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>16560542</v>
       </c>
       <c r="BA15" t="n">
-        <v>2560187</v>
+        <v>21276462</v>
       </c>
       <c r="BB15" t="n">
-        <v>2560187</v>
+        <v>38328962</v>
       </c>
       <c r="BC15" t="n">
-        <v>2560187</v>
+        <v>38328962</v>
       </c>
       <c r="BD15" t="n">
         <v>0</v>
@@ -4083,10 +4083,10 @@
         <v>0</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>2255167</v>
       </c>
       <c r="BO15" t="n">
-        <v>2560187</v>
+        <v>21276462</v>
       </c>
       <c r="BP15" t="n">
         <v>2</v>
@@ -4095,22 +4095,22 @@
         <v>0</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STEL</t>
+          <t>ASAHISONG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>STEL HOLDINGS LIMITED</t>
+          <t>ASAHI SONGWON COLORS LIMITED</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4118,40 +4118,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G16" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H16" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>619.3</v>
+        <v>402.75</v>
       </c>
       <c r="J16" t="n">
-        <v>636.71</v>
+        <v>338.1</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.7</v>
+        <v>19.1</v>
       </c>
       <c r="L16" t="n">
-        <v>64.68000000000001</v>
+        <v>66.73</v>
       </c>
       <c r="M16" t="n">
-        <v>4.12</v>
+        <v>0.34</v>
       </c>
       <c r="N16" t="n">
-        <v>41238002</v>
+        <v>3381000</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>41238002</v>
+        <v>3381000</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -4165,124 +4165,124 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="V16" t="n">
-        <v>0.356</v>
+        <v>0.074</v>
       </c>
       <c r="W16" t="n">
-        <v>1160</v>
+        <v>458</v>
       </c>
       <c r="X16" t="n">
-        <v>59.1</v>
+        <v>13.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>21</v>
+        <v>-8</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.11</v>
+        <v>24</v>
       </c>
       <c r="AA16" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0.07000000000000001</v>
+        <v>14.36</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.58</v>
+        <v>9.94</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="AE16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF16" t="n">
-        <v>-110</v>
+        <v>18</v>
       </c>
       <c r="AG16" t="n">
-        <v>590.22</v>
+        <v>359.64</v>
       </c>
       <c r="AH16" t="n">
-        <v>518.25</v>
+        <v>270.07</v>
       </c>
       <c r="AI16" t="n">
-        <v>45.3</v>
+        <v>101.1</v>
       </c>
       <c r="AJ16" t="n">
-        <v>636.7131718313339</v>
+        <v>338.1</v>
       </c>
       <c r="AK16" t="n">
-        <v>-2.7</v>
+        <v>19.1</v>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="AQ16" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="AS16" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="AT16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="AX16" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="AY16" t="n">
-        <v>2255167</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>16560542</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>21276462</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>38328962</v>
+        <v>3381000</v>
       </c>
       <c r="BC16" t="n">
-        <v>38328962</v>
+        <v>3381000</v>
       </c>
       <c r="BD16" t="n">
         <v>0</v>
@@ -4315,45 +4315,45 @@
         <v>0</v>
       </c>
       <c r="BN16" t="n">
-        <v>2255167</v>
+        <v>0</v>
       </c>
       <c r="BO16" t="n">
-        <v>21276462</v>
+        <v>0</v>
       </c>
       <c r="BP16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ16" t="n">
         <v>0</v>
       </c>
       <c r="BR16" t="n">
-        <v>0.106</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ASAHISONG</t>
+          <t>JAYAGROGN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ASAHI SONGWON COLORS LIMITED</t>
+          <t>Jayant Agro-Organics Limited</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Watchlist</t>
+          <t>Fundamental Watch</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G17" t="n">
         <v>21</v>
@@ -4362,28 +4362,28 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>402.75</v>
+        <v>234.84</v>
       </c>
       <c r="J17" t="n">
-        <v>338.1</v>
+        <v>234.4</v>
       </c>
       <c r="K17" t="n">
-        <v>19.1</v>
+        <v>0.2</v>
       </c>
       <c r="L17" t="n">
-        <v>66.73</v>
+        <v>67.13</v>
       </c>
       <c r="M17" t="n">
-        <v>0.34</v>
+        <v>0.3</v>
       </c>
       <c r="N17" t="n">
-        <v>3381000</v>
+        <v>2995877</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3381000</v>
+        <v>2995877</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -4397,124 +4397,124 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>23-09-2026</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="W17" t="n">
+        <v>695</v>
+      </c>
+      <c r="X17" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA17" t="n">
         <v>1</v>
       </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>11-08-2026</t>
-        </is>
-      </c>
-      <c r="V17" t="n">
-        <v>0.073</v>
-      </c>
-      <c r="W17" t="n">
-        <v>461</v>
-      </c>
-      <c r="X17" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>-8</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>33</v>
-      </c>
       <c r="AB17" t="n">
-        <v>14.36</v>
+        <v>6.54</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.94</v>
+        <v>14.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.23</v>
+        <v>0.11</v>
       </c>
       <c r="AE17" t="b">
         <v>1</v>
       </c>
       <c r="AF17" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="AG17" t="n">
-        <v>359.64</v>
+        <v>227.7</v>
       </c>
       <c r="AH17" t="n">
-        <v>270.07</v>
+        <v>205.16</v>
       </c>
       <c r="AI17" t="n">
-        <v>101.1</v>
+        <v>40.7</v>
       </c>
       <c r="AJ17" t="n">
-        <v>338.1</v>
+        <v>234.4008293560754</v>
       </c>
       <c r="AK17" t="n">
-        <v>19.1</v>
+        <v>0.2</v>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR17" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="AS17" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AX17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1358248</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>2995877</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>2995877</v>
       </c>
       <c r="BB17" t="n">
-        <v>3381000</v>
+        <v>2995877</v>
       </c>
       <c r="BC17" t="n">
-        <v>3381000</v>
+        <v>2995877</v>
       </c>
       <c r="BD17" t="n">
         <v>0</v>
@@ -4547,10 +4547,10 @@
         <v>0</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>1358248</v>
       </c>
       <c r="BO17" t="n">
-        <v>0</v>
+        <v>2995877</v>
       </c>
       <c r="BP17" t="n">
         <v>1</v>
@@ -4559,18 +4559,18 @@
         <v>0</v>
       </c>
       <c r="BR17" t="n">
-        <v>0</v>
+        <v>0.4534</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JAYAGROGN</t>
+          <t>CHEMBOND</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jayant Agro-Organics Limited</t>
+          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -4582,40 +4582,40 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
         <v>12</v>
       </c>
       <c r="G18" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I18" t="n">
-        <v>234.84</v>
+        <v>191.99</v>
       </c>
       <c r="J18" t="n">
-        <v>234.4</v>
+        <v>170.45</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2</v>
+        <v>12.6</v>
       </c>
       <c r="L18" t="n">
-        <v>67.13</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3</v>
+        <v>0.26</v>
       </c>
       <c r="N18" t="n">
-        <v>2995877</v>
+        <v>2560187</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2995877</v>
+        <v>2560187</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -4629,124 +4629,124 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="V18" t="n">
-        <v>0.043</v>
+        <v>0.099</v>
       </c>
       <c r="W18" t="n">
-        <v>689</v>
+        <v>258</v>
       </c>
       <c r="X18" t="n">
-        <v>11.2</v>
+        <v>27.6</v>
       </c>
       <c r="Y18" t="n">
-        <v>-5</v>
+        <v>24</v>
       </c>
       <c r="Z18" t="n">
-        <v>32</v>
+        <v>1.87</v>
       </c>
       <c r="AA18" t="n">
-        <v>1</v>
+        <v>-31</v>
       </c>
       <c r="AB18" t="n">
-        <v>6.54</v>
+        <v>3.36</v>
       </c>
       <c r="AC18" t="n">
-        <v>14.8</v>
+        <v>4.96</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>1</v>
       </c>
       <c r="AF18" t="n">
-        <v>9</v>
+        <v>2.97</v>
       </c>
       <c r="AG18" t="n">
-        <v>227.7</v>
+        <v>181.14</v>
       </c>
       <c r="AH18" t="n">
-        <v>205.16</v>
+        <v>163.73</v>
       </c>
       <c r="AI18" t="n">
-        <v>40.7</v>
+        <v>57.4</v>
       </c>
       <c r="AJ18" t="n">
-        <v>234.4008293560754</v>
+        <v>170.4518641810919</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.2</v>
+        <v>12.6</v>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
         <v>2</v>
       </c>
-      <c r="AR18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT18" t="n">
+      <c r="AW18" t="n">
         <v>2</v>
       </c>
-      <c r="AU18" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>3</v>
-      </c>
       <c r="AX18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY18" t="n">
-        <v>1358248</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>2995877</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>2995877</v>
+        <v>2560187</v>
       </c>
       <c r="BB18" t="n">
-        <v>2995877</v>
+        <v>2560187</v>
       </c>
       <c r="BC18" t="n">
-        <v>2995877</v>
+        <v>2560187</v>
       </c>
       <c r="BD18" t="n">
         <v>0</v>
@@ -4779,19 +4779,19 @@
         <v>0</v>
       </c>
       <c r="BN18" t="n">
-        <v>1358248</v>
+        <v>0</v>
       </c>
       <c r="BO18" t="n">
-        <v>2995877</v>
+        <v>2560187</v>
       </c>
       <c r="BP18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ18" t="n">
         <v>0</v>
       </c>
       <c r="BR18" t="n">
-        <v>0.4534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -4869,13 +4869,13 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>2.844</v>
+        <v>2.864</v>
       </c>
       <c r="W19" t="n">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="X19" t="n">
-        <v>26</v>
+        <v>25.9</v>
       </c>
       <c r="Y19" t="n">
         <v>30</v>
@@ -5095,13 +5095,13 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>0.633</v>
+        <v>0.645</v>
       </c>
       <c r="W20" t="n">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="X20" t="n">
-        <v>1196</v>
+        <v>1175</v>
       </c>
       <c r="Y20" t="n">
         <v>-61</v>
@@ -5323,13 +5323,13 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>0.267</v>
+        <v>0.273</v>
       </c>
       <c r="W21" t="n">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="X21" t="n">
-        <v>38.7</v>
+        <v>38</v>
       </c>
       <c r="Y21" t="n">
         <v>-44</v>
@@ -5555,13 +5555,13 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>0.497</v>
+        <v>0.494</v>
       </c>
       <c r="W22" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="X22" t="n">
-        <v>37.3</v>
+        <v>37.5</v>
       </c>
       <c r="Y22" t="n">
         <v>21</v>
@@ -5790,10 +5790,10 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="X23" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="Y23" t="n">
         <v>19</v>
@@ -5945,12 +5945,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SGIL</t>
+          <t>CHEMBONDCH</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
+          <t>CHEMBOND CHEMICALS LIMITED</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -5962,40 +5962,40 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F24" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G24" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>642.5</v>
+        <v>254.95</v>
       </c>
       <c r="J24" t="n">
-        <v>593.62</v>
+        <v>243.52</v>
       </c>
       <c r="K24" t="n">
-        <v>8.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="L24" t="n">
-        <v>74.02</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>0.25</v>
+        <v>1.11</v>
       </c>
       <c r="N24" t="n">
-        <v>2458195</v>
+        <v>11080000</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2458195</v>
+        <v>11080000</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -6013,88 +6013,90 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="V24" t="n">
-        <v>0.024</v>
+        <v>0.166</v>
       </c>
       <c r="W24" t="n">
-        <v>1010</v>
-      </c>
-      <c r="X24" t="inlineStr"/>
+        <v>668</v>
+      </c>
+      <c r="X24" t="n">
+        <v>55.8</v>
+      </c>
       <c r="Y24" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="Z24" t="n">
-        <v>5</v>
+        <v>2.99</v>
       </c>
       <c r="AA24" t="n">
-        <v>-152</v>
+        <v>97</v>
       </c>
       <c r="AB24" t="n">
-        <v>-6.5</v>
+        <v>1</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.24</v>
+        <v>11.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.23</v>
+        <v>-0</v>
       </c>
       <c r="AE24" t="b">
         <v>1</v>
       </c>
       <c r="AF24" t="n">
-        <v>6</v>
+        <v>16.21</v>
       </c>
       <c r="AG24" t="n">
-        <v>594.98</v>
+        <v>255.87</v>
       </c>
       <c r="AH24" t="n">
-        <v>548</v>
+        <v>188.4</v>
       </c>
       <c r="AI24" t="n">
-        <v>32.3</v>
+        <v>113.3</v>
       </c>
       <c r="AJ24" t="n">
-        <v>593.6235208886742</v>
+        <v>243.5164835164835</v>
       </c>
       <c r="AK24" t="n">
-        <v>8.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="AQ24" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AR24" t="n">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="AS24" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="AT24" t="n">
         <v>0</v>
@@ -6103,7 +6105,7 @@
         <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
         <v>3</v>
@@ -6118,13 +6120,13 @@
         <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>1288195</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>2458195</v>
+        <v>11080000</v>
       </c>
       <c r="BC24" t="n">
-        <v>2458195</v>
+        <v>11080000</v>
       </c>
       <c r="BD24" t="n">
         <v>0</v>
@@ -6160,10 +6162,10 @@
         <v>0</v>
       </c>
       <c r="BO24" t="n">
-        <v>1288195</v>
+        <v>0</v>
       </c>
       <c r="BP24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BQ24" t="n">
         <v>0</v>
@@ -6175,12 +6177,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CHEMBONDCH</t>
+          <t>SGIL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CHEMBOND CHEMICALS LIMITED</t>
+          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -6192,40 +6194,40 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F25" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G25" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>254.95</v>
+        <v>642.5</v>
       </c>
       <c r="J25" t="n">
-        <v>243.52</v>
+        <v>593.62</v>
       </c>
       <c r="K25" t="n">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>67.65000000000001</v>
+        <v>74.02</v>
       </c>
       <c r="M25" t="n">
-        <v>1.11</v>
+        <v>0.25</v>
       </c>
       <c r="N25" t="n">
-        <v>11080000</v>
+        <v>2458195</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>11080000</v>
+        <v>2458195</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -6243,90 +6245,88 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="V25" t="n">
-        <v>0.162</v>
+        <v>0.025</v>
       </c>
       <c r="W25" t="n">
-        <v>685</v>
-      </c>
-      <c r="X25" t="n">
-        <v>57.2</v>
-      </c>
+        <v>994</v>
+      </c>
+      <c r="X25" t="inlineStr"/>
       <c r="Y25" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.99</v>
+        <v>5</v>
       </c>
       <c r="AA25" t="n">
-        <v>97</v>
+        <v>-152</v>
       </c>
       <c r="AB25" t="n">
-        <v>1</v>
+        <v>-6.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>11.6</v>
+        <v>9.24</v>
       </c>
       <c r="AD25" t="n">
-        <v>-0</v>
+        <v>2.23</v>
       </c>
       <c r="AE25" t="b">
         <v>1</v>
       </c>
       <c r="AF25" t="n">
-        <v>16.21</v>
+        <v>6</v>
       </c>
       <c r="AG25" t="n">
-        <v>255.87</v>
+        <v>594.98</v>
       </c>
       <c r="AH25" t="n">
-        <v>188.4</v>
+        <v>548</v>
       </c>
       <c r="AI25" t="n">
-        <v>113.3</v>
+        <v>32.3</v>
       </c>
       <c r="AJ25" t="n">
-        <v>243.5164835164835</v>
+        <v>593.6235208886742</v>
       </c>
       <c r="AK25" t="n">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="AQ25" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AR25" t="n">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="AS25" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="AT25" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
         <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW25" t="n">
         <v>3</v>
@@ -6350,13 +6350,13 @@
         <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1288195</v>
       </c>
       <c r="BB25" t="n">
-        <v>11080000</v>
+        <v>2458195</v>
       </c>
       <c r="BC25" t="n">
-        <v>11080000</v>
+        <v>2458195</v>
       </c>
       <c r="BD25" t="n">
         <v>0</v>
@@ -6392,10 +6392,10 @@
         <v>0</v>
       </c>
       <c r="BO25" t="n">
-        <v>0</v>
+        <v>1288195</v>
       </c>
       <c r="BP25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BQ25" t="n">
         <v>0</v>
@@ -6479,13 +6479,13 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>0.057</v>
+        <v>0.059</v>
       </c>
       <c r="W26" t="n">
-        <v>1916</v>
+        <v>1876</v>
       </c>
       <c r="X26" t="n">
-        <v>44</v>
+        <v>43.1</v>
       </c>
       <c r="Y26" t="n">
         <v>20</v>
@@ -6714,7 +6714,7 @@
         <v>0.05</v>
       </c>
       <c r="W27" t="n">
-        <v>5231</v>
+        <v>5225</v>
       </c>
       <c r="X27" t="n">
         <v>34.1</v>
@@ -6946,10 +6946,10 @@
         <v>0.132</v>
       </c>
       <c r="W28" t="n">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="X28" t="n">
-        <v>6.1</v>
+        <v>6.06</v>
       </c>
       <c r="Y28" t="n">
         <v>118</v>
@@ -7171,13 +7171,13 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>0.866</v>
+        <v>0.893</v>
       </c>
       <c r="W29" t="n">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="X29" t="n">
-        <v>6.7</v>
+        <v>6.49</v>
       </c>
       <c r="Y29" t="n">
         <v>31</v>
@@ -7399,13 +7399,13 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>0.644</v>
+        <v>0.643</v>
       </c>
       <c r="W30" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="X30" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="Y30" t="n">
         <v>19</v>
@@ -7631,13 +7631,13 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>0.039</v>
+        <v>0.04</v>
       </c>
       <c r="W31" t="n">
-        <v>3423</v>
+        <v>3400</v>
       </c>
       <c r="X31" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="Y31" t="n">
         <v>-4</v>
@@ -7866,10 +7866,10 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="W32" t="n">
-        <v>53455</v>
+        <v>52622</v>
       </c>
       <c r="X32" t="n">
-        <v>45.2</v>
+        <v>44.5</v>
       </c>
       <c r="Y32" t="n">
         <v>5</v>
@@ -8330,10 +8330,10 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>3527</v>
+        <v>3432</v>
       </c>
       <c r="X34" t="n">
-        <v>79.40000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="Y34" t="n">
         <v>42</v>
@@ -8559,10 +8559,10 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
       <c r="W35" t="n">
-        <v>9522</v>
+        <v>9580</v>
       </c>
       <c r="X35" t="n">
         <v>12.6</v>
@@ -9020,10 +9020,10 @@
         <v>0.008</v>
       </c>
       <c r="W37" t="n">
-        <v>5218</v>
+        <v>5105</v>
       </c>
       <c r="X37" t="n">
-        <v>8.82</v>
+        <v>8.66</v>
       </c>
       <c r="Y37" t="n">
         <v>43</v>
@@ -9249,13 +9249,13 @@
         </is>
       </c>
       <c r="V38" t="n">
-        <v>0.217</v>
+        <v>0.223</v>
       </c>
       <c r="W38" t="n">
-        <v>644</v>
+        <v>629</v>
       </c>
       <c r="X38" t="n">
-        <v>14.2</v>
+        <v>13.9</v>
       </c>
       <c r="Y38" t="n">
         <v>-1</v>
@@ -9481,10 +9481,10 @@
         </is>
       </c>
       <c r="V39" t="n">
-        <v>0.211</v>
+        <v>0.212</v>
       </c>
       <c r="W39" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="X39" t="n">
         <v>25.3</v>
@@ -9713,13 +9713,13 @@
         </is>
       </c>
       <c r="V40" t="n">
-        <v>0.214</v>
+        <v>0.216</v>
       </c>
       <c r="W40" t="n">
-        <v>957</v>
+        <v>948</v>
       </c>
       <c r="X40" t="n">
-        <v>26.1</v>
+        <v>25.8</v>
       </c>
       <c r="Y40" t="n">
         <v>9</v>
@@ -9945,13 +9945,13 @@
         </is>
       </c>
       <c r="V41" t="n">
-        <v>0.219</v>
+        <v>0.216</v>
       </c>
       <c r="W41" t="n">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="X41" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="Y41" t="n">
         <v>16</v>
@@ -10180,10 +10180,10 @@
         <v>0.074</v>
       </c>
       <c r="W42" t="n">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="X42" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="Y42" t="n">
         <v>185</v>
@@ -10410,7 +10410,7 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>8932</v>
+        <v>8896</v>
       </c>
       <c r="X43" t="n">
         <v>15.2</v>
@@ -10639,13 +10639,13 @@
         </is>
       </c>
       <c r="V44" t="n">
-        <v>0.674</v>
+        <v>0.678</v>
       </c>
       <c r="W44" t="n">
-        <v>3864</v>
+        <v>3836</v>
       </c>
       <c r="X44" t="n">
-        <v>27</v>
+        <v>26.9</v>
       </c>
       <c r="Y44" t="n">
         <v>2</v>
@@ -10874,7 +10874,7 @@
         <v>0.227</v>
       </c>
       <c r="W45" t="n">
-        <v>1758</v>
+        <v>1756</v>
       </c>
       <c r="X45" t="n">
         <v>18.6</v>
@@ -11106,10 +11106,10 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>117300</v>
+        <v>116035</v>
       </c>
       <c r="X46" t="n">
-        <v>33.8</v>
+        <v>33.4</v>
       </c>
       <c r="Y46" t="n">
         <v>18</v>
@@ -11341,7 +11341,7 @@
         <v>389</v>
       </c>
       <c r="X47" t="n">
-        <v>96.40000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="Y47" t="n">
         <v>246</v>
@@ -11570,10 +11570,10 @@
         <v>0.044</v>
       </c>
       <c r="W48" t="n">
-        <v>1589</v>
+        <v>1571</v>
       </c>
       <c r="X48" t="n">
-        <v>20.8</v>
+        <v>20.5</v>
       </c>
       <c r="Y48" t="n">
         <v>10</v>
@@ -11799,13 +11799,13 @@
         </is>
       </c>
       <c r="V49" t="n">
-        <v>0.082</v>
+        <v>0.083</v>
       </c>
       <c r="W49" t="n">
-        <v>1659</v>
+        <v>1650</v>
       </c>
       <c r="X49" t="n">
-        <v>30</v>
+        <v>29.8</v>
       </c>
       <c r="Y49" t="n">
         <v>39</v>
@@ -12078,23 +12078,23 @@
         <v>351.5</v>
       </c>
       <c r="D3" t="n">
-        <v>324.91</v>
+        <v>326.23</v>
       </c>
       <c r="E3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="F3" t="n">
         <v>63.24</v>
       </c>
       <c r="G3" t="n">
-        <v>2.83</v>
+        <v>3.02</v>
       </c>
       <c r="H3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>25-09-2026</t>
         </is>
       </c>
     </row>
@@ -12206,70 +12206,70 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ALEMBICLTD</t>
+          <t>INDORAMA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alembic Limited</t>
+          <t>INDO RAMA SYNTHETICS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>106.53</v>
+        <v>99.36</v>
       </c>
       <c r="D7" t="n">
-        <v>95.19</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>11.9</v>
+        <v>31.3</v>
       </c>
       <c r="F7" t="n">
-        <v>70.88</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>12.18</v>
+        <v>3.14</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>INDORAMA</t>
+          <t>ALEMBICLTD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>INDO RAMA SYNTHETICS (INDIA) LIMITED</t>
+          <t>Alembic Limited</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>99.36</v>
+        <v>106.53</v>
       </c>
       <c r="D8" t="n">
-        <v>75.68000000000001</v>
+        <v>95.19</v>
       </c>
       <c r="E8" t="n">
-        <v>31.3</v>
+        <v>11.9</v>
       </c>
       <c r="F8" t="n">
-        <v>74.84999999999999</v>
+        <v>70.88</v>
       </c>
       <c r="G8" t="n">
-        <v>3.14</v>
+        <v>12.18</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
     </row>
@@ -12486,140 +12486,140 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CHEMBOND</t>
+          <t>STEL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
+          <t>STEL HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>191.99</v>
+        <v>619.3</v>
       </c>
       <c r="D15" t="n">
-        <v>170.45</v>
+        <v>636.71</v>
       </c>
       <c r="E15" t="n">
-        <v>12.6</v>
+        <v>-2.7</v>
       </c>
       <c r="F15" t="n">
-        <v>67.54000000000001</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>0.26</v>
+        <v>4.12</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STEL</t>
+          <t>ASAHISONG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>STEL HOLDINGS LIMITED</t>
+          <t>ASAHI SONGWON COLORS LIMITED</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>619.3</v>
+        <v>402.75</v>
       </c>
       <c r="D16" t="n">
-        <v>636.71</v>
+        <v>338.1</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.7</v>
+        <v>19.1</v>
       </c>
       <c r="F16" t="n">
-        <v>64.68000000000001</v>
+        <v>66.73</v>
       </c>
       <c r="G16" t="n">
-        <v>4.12</v>
+        <v>0.34</v>
       </c>
       <c r="H16" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ASAHISONG</t>
+          <t>JAYAGROGN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ASAHI SONGWON COLORS LIMITED</t>
+          <t>Jayant Agro-Organics Limited</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>402.75</v>
+        <v>234.84</v>
       </c>
       <c r="D17" t="n">
-        <v>338.1</v>
+        <v>234.4</v>
       </c>
       <c r="E17" t="n">
-        <v>19.1</v>
+        <v>0.2</v>
       </c>
       <c r="F17" t="n">
-        <v>66.73</v>
+        <v>67.13</v>
       </c>
       <c r="G17" t="n">
-        <v>0.34</v>
+        <v>0.3</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JAYAGROGN</t>
+          <t>CHEMBOND</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jayant Agro-Organics Limited</t>
+          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>234.84</v>
+        <v>191.99</v>
       </c>
       <c r="D18" t="n">
-        <v>234.4</v>
+        <v>170.45</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2</v>
+        <v>12.6</v>
       </c>
       <c r="F18" t="n">
-        <v>67.13</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3</v>
+        <v>0.26</v>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
     </row>
@@ -12801,70 +12801,70 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SGIL</t>
+          <t>CHEMBONDCH</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
+          <t>CHEMBOND CHEMICALS LIMITED</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>642.5</v>
+        <v>254.95</v>
       </c>
       <c r="D24" t="n">
-        <v>593.62</v>
+        <v>243.52</v>
       </c>
       <c r="E24" t="n">
-        <v>8.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="F24" t="n">
-        <v>74.02</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>0.25</v>
+        <v>1.11</v>
       </c>
       <c r="H24" t="n">
         <v>3</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CHEMBONDCH</t>
+          <t>SGIL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CHEMBOND CHEMICALS LIMITED</t>
+          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>254.95</v>
+        <v>642.5</v>
       </c>
       <c r="D25" t="n">
-        <v>243.52</v>
+        <v>593.62</v>
       </c>
       <c r="E25" t="n">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>67.65000000000001</v>
+        <v>74.02</v>
       </c>
       <c r="G25" t="n">
-        <v>1.11</v>
+        <v>0.25</v>
       </c>
       <c r="H25" t="n">
         <v>3</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
     </row>
@@ -13811,7 +13811,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -13831,7 +13831,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/output/2026-09-28/enriched_analysis.xlsx
+++ b/output/2026-09-28/enriched_analysis.xlsx
@@ -6641,12 +6641,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AFFORDABLE</t>
+          <t>HEXAGON</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
+          <t>HEXAGON NUTRITION LIMITED</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -6658,171 +6658,169 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F27" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G27" t="n">
+        <v>5</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>64.34999999999999</v>
+      </c>
+      <c r="J27" t="n">
+        <v>64.48999999999999</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="L27" t="n">
+        <v>64.29000000000001</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="N27" t="n">
+        <v>5656038</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>5656038</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
         <v>9</v>
       </c>
-      <c r="H27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I27" t="n">
-        <v>170.74</v>
-      </c>
-      <c r="J27" t="n">
-        <v>169.88</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L27" t="n">
-        <v>61.48</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N27" t="n">
-        <v>5988193</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>5988193</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S27" t="b">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>5</v>
-      </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
       <c r="V27" t="n">
-        <v>0.277</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="W27" t="n">
-        <v>216</v>
+        <v>794</v>
       </c>
       <c r="X27" t="n">
-        <v>37.5</v>
+        <v>20.1</v>
       </c>
       <c r="Y27" t="n">
-        <v>-44</v>
+        <v>19</v>
       </c>
       <c r="Z27" t="n">
-        <v>-3.28</v>
+        <v>12.31</v>
       </c>
       <c r="AA27" t="n">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="AB27" t="n">
-        <v>-4.05</v>
+        <v>0.8</v>
       </c>
       <c r="AC27" t="n">
-        <v>8.25</v>
+        <v>22.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.44</v>
+        <v>0.11</v>
       </c>
       <c r="AE27" t="b">
         <v>1</v>
       </c>
       <c r="AF27" t="n">
-        <v>-35.96</v>
+        <v>12.14</v>
       </c>
       <c r="AG27" t="n">
-        <v>173.9</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>178.81</v>
-      </c>
+        <v>66.16</v>
+      </c>
+      <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="n">
-        <v>19.8</v>
+        <v>27</v>
       </c>
       <c r="AJ27" t="n">
-        <v>169.8778156028369</v>
+        <v>64.49302166476625</v>
       </c>
       <c r="AK27" t="n">
-        <v>0.5</v>
+        <v>-0.2</v>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
       <c r="AQ27" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="AR27" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="AS27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AT27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW27" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AX27" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AY27" t="n">
-        <v>2000469</v>
+        <v>0</v>
       </c>
       <c r="AZ27" t="n">
-        <v>5988193</v>
+        <v>2601121</v>
       </c>
       <c r="BA27" t="n">
-        <v>5988193</v>
+        <v>2601121</v>
       </c>
       <c r="BB27" t="n">
-        <v>5988193</v>
+        <v>5656038</v>
       </c>
       <c r="BC27" t="n">
-        <v>5988193</v>
+        <v>5656038</v>
       </c>
       <c r="BD27" t="n">
         <v>0</v>
@@ -6855,30 +6853,30 @@
         <v>0</v>
       </c>
       <c r="BN27" t="n">
-        <v>2000469</v>
+        <v>0</v>
       </c>
       <c r="BO27" t="n">
-        <v>5988193</v>
+        <v>2601121</v>
       </c>
       <c r="BP27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BQ27" t="n">
         <v>0</v>
       </c>
       <c r="BR27" t="n">
-        <v>0.3341</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>HEXAGON</t>
+          <t>SRGHFL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HEXAGON NUTRITION LIMITED</t>
+          <t>SRG HOUSING FINANCE LIMITED</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -6890,40 +6888,40 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F28" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G28" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>64.34999999999999</v>
+        <v>140.95</v>
       </c>
       <c r="J28" t="n">
-        <v>64.48999999999999</v>
+        <v>132.2</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.2</v>
+        <v>6.6</v>
       </c>
       <c r="L28" t="n">
-        <v>64.29000000000001</v>
+        <v>67.83</v>
       </c>
       <c r="M28" t="n">
-        <v>0.57</v>
+        <v>1.98</v>
       </c>
       <c r="N28" t="n">
-        <v>5656038</v>
+        <v>19830410</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>5656038</v>
+        <v>19830410</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -6937,122 +6935,120 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
       <c r="V28" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.893</v>
       </c>
       <c r="W28" t="n">
-        <v>794</v>
+        <v>222</v>
       </c>
       <c r="X28" t="n">
-        <v>20.1</v>
+        <v>6.51</v>
       </c>
       <c r="Y28" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>12.31</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.8</v>
+        <v>5.39</v>
       </c>
       <c r="AC28" t="n">
-        <v>22.2</v>
+        <v>11.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.11</v>
+        <v>2.89</v>
       </c>
       <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="n">
+        <v>244.04</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>269.09</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>-39.6</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>132.2027333333333</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN28" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>15-09-2026</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>16-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ28" t="n">
         <v>1</v>
       </c>
-      <c r="AF28" t="n">
-        <v>12.14</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>66.16</v>
-      </c>
-      <c r="AH28" t="inlineStr"/>
-      <c r="AI28" t="n">
-        <v>27</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>64.49302166476625</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AL28" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>17-08-2026</t>
-        </is>
-      </c>
-      <c r="AP28" t="inlineStr">
-        <is>
-          <t>18-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ28" t="n">
-        <v>32</v>
-      </c>
       <c r="AR28" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="AS28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AT28" t="n">
         <v>0</v>
       </c>
       <c r="AU28" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AV28" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AW28" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AX28" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AY28" t="n">
         <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>2601121</v>
+        <v>19830410</v>
       </c>
       <c r="BA28" t="n">
-        <v>2601121</v>
+        <v>19830410</v>
       </c>
       <c r="BB28" t="n">
-        <v>5656038</v>
+        <v>19830410</v>
       </c>
       <c r="BC28" t="n">
-        <v>5656038</v>
+        <v>19830410</v>
       </c>
       <c r="BD28" t="n">
         <v>0</v>
@@ -7088,10 +7084,10 @@
         <v>0</v>
       </c>
       <c r="BO28" t="n">
-        <v>2601121</v>
+        <v>19830410</v>
       </c>
       <c r="BP28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BQ28" t="n">
         <v>0</v>
@@ -7103,16 +7099,16 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SRGHFL</t>
+          <t>CHEMBONDCH</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SRG HOUSING FINANCE LIMITED</t>
+          <t>CHEMBOND CHEMICALS LIMITED</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -7120,40 +7116,40 @@
         </is>
       </c>
       <c r="E29" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" t="n">
         <v>14</v>
       </c>
-      <c r="F29" t="n">
-        <v>10</v>
-      </c>
       <c r="G29" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>140.95</v>
+        <v>242.4</v>
       </c>
       <c r="J29" t="n">
-        <v>132.2</v>
+        <v>243.52</v>
       </c>
       <c r="K29" t="n">
-        <v>6.6</v>
+        <v>-0.5</v>
       </c>
       <c r="L29" t="n">
-        <v>67.83</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>1.98</v>
+        <v>1.11</v>
       </c>
       <c r="N29" t="n">
-        <v>19830410</v>
+        <v>11080000</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>19830410</v>
+        <v>11080000</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -7171,95 +7167,99 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="V29" t="n">
-        <v>0.893</v>
+        <v>0.174</v>
       </c>
       <c r="W29" t="n">
-        <v>222</v>
+        <v>636</v>
       </c>
       <c r="X29" t="n">
-        <v>6.51</v>
+        <v>53.1</v>
       </c>
       <c r="Y29" t="n">
-        <v>31</v>
-      </c>
-      <c r="Z29" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.99</v>
+      </c>
       <c r="AA29" t="n">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="AB29" t="n">
-        <v>5.39</v>
+        <v>1</v>
       </c>
       <c r="AC29" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>16.21</v>
+      </c>
       <c r="AG29" t="n">
-        <v>244.04</v>
+        <v>255.88</v>
       </c>
       <c r="AH29" t="n">
-        <v>269.09</v>
+        <v>188.87</v>
       </c>
       <c r="AI29" t="n">
-        <v>-39.6</v>
+        <v>104.6</v>
       </c>
       <c r="AJ29" t="n">
-        <v>132.2027333333333</v>
+        <v>243.5164835164835</v>
       </c>
       <c r="AK29" t="n">
-        <v>6.6</v>
+        <v>-0.5</v>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>15-09-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="AQ29" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="AR29" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="AS29" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="AT29" t="n">
         <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
         <v>3</v>
@@ -7271,16 +7271,16 @@
         <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>19830410</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>19830410</v>
+        <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>19830410</v>
+        <v>11080000</v>
       </c>
       <c r="BC29" t="n">
-        <v>19830410</v>
+        <v>11080000</v>
       </c>
       <c r="BD29" t="n">
         <v>0</v>
@@ -7316,7 +7316,7 @@
         <v>0</v>
       </c>
       <c r="BO29" t="n">
-        <v>19830410</v>
+        <v>0</v>
       </c>
       <c r="BP29" t="n">
         <v>2</v>
@@ -7331,16 +7331,16 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CHEMBONDCH</t>
+          <t>AFFORDABLE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CHEMBOND CHEMICALS LIMITED</t>
+          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -7348,40 +7348,40 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F30" t="n">
         <v>14</v>
       </c>
       <c r="G30" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I30" t="n">
-        <v>242.4</v>
+        <v>170.74</v>
       </c>
       <c r="J30" t="n">
-        <v>243.52</v>
+        <v>174.27</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.5</v>
+        <v>-2</v>
       </c>
       <c r="L30" t="n">
-        <v>67.65000000000001</v>
+        <v>61.48</v>
       </c>
       <c r="M30" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="N30" t="n">
-        <v>11080000</v>
+        <v>10743104</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>11080000</v>
+        <v>10743104</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -7395,124 +7395,124 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="V30" t="n">
-        <v>0.174</v>
+        <v>0.497</v>
       </c>
       <c r="W30" t="n">
-        <v>636</v>
+        <v>216</v>
       </c>
       <c r="X30" t="n">
-        <v>53.1</v>
+        <v>37.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>3</v>
+        <v>-44</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.99</v>
+        <v>-3.28</v>
       </c>
       <c r="AA30" t="n">
-        <v>97</v>
+        <v>141</v>
       </c>
       <c r="AB30" t="n">
-        <v>1</v>
+        <v>-4.05</v>
       </c>
       <c r="AC30" t="n">
-        <v>11.6</v>
+        <v>8.25</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="AE30" t="b">
         <v>1</v>
       </c>
       <c r="AF30" t="n">
-        <v>16.21</v>
+        <v>-35.96</v>
       </c>
       <c r="AG30" t="n">
-        <v>255.88</v>
+        <v>173.9</v>
       </c>
       <c r="AH30" t="n">
-        <v>188.87</v>
+        <v>178.81</v>
       </c>
       <c r="AI30" t="n">
-        <v>104.6</v>
+        <v>19.8</v>
       </c>
       <c r="AJ30" t="n">
-        <v>243.5164835164835</v>
+        <v>174.2652478588113</v>
       </c>
       <c r="AK30" t="n">
-        <v>-0.5</v>
+        <v>-2</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="AQ30" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="AR30" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="AS30" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AW30" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AX30" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>6755380</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>10743104</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>10743104</v>
       </c>
       <c r="BB30" t="n">
-        <v>11080000</v>
+        <v>10743104</v>
       </c>
       <c r="BC30" t="n">
-        <v>11080000</v>
+        <v>10743104</v>
       </c>
       <c r="BD30" t="n">
         <v>0</v>
@@ -7545,19 +7545,19 @@
         <v>0</v>
       </c>
       <c r="BN30" t="n">
-        <v>0</v>
+        <v>6755380</v>
       </c>
       <c r="BO30" t="n">
-        <v>0</v>
+        <v>10743104</v>
       </c>
       <c r="BP30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ30" t="n">
         <v>0</v>
       </c>
       <c r="BR30" t="n">
-        <v>0</v>
+        <v>0.6288</v>
       </c>
     </row>
     <row r="31">
@@ -13138,140 +13138,140 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AFFORDABLE</t>
+          <t>HEXAGON</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
+          <t>HEXAGON NUTRITION LIMITED</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>170.74</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>169.88</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5</v>
+        <v>-0.2</v>
       </c>
       <c r="F27" t="n">
-        <v>61.48</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="H27" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>HEXAGON</t>
+          <t>SRGHFL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HEXAGON NUTRITION LIMITED</t>
+          <t>SRG HOUSING FINANCE LIMITED</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>64.34999999999999</v>
+        <v>140.95</v>
       </c>
       <c r="D28" t="n">
-        <v>64.48999999999999</v>
+        <v>132.2</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.2</v>
+        <v>6.6</v>
       </c>
       <c r="F28" t="n">
-        <v>64.29000000000001</v>
+        <v>67.83</v>
       </c>
       <c r="G28" t="n">
-        <v>0.57</v>
+        <v>1.98</v>
       </c>
       <c r="H28" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SRGHFL</t>
+          <t>CHEMBONDCH</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SRG HOUSING FINANCE LIMITED</t>
+          <t>CHEMBOND CHEMICALS LIMITED</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>140.95</v>
+        <v>242.4</v>
       </c>
       <c r="D29" t="n">
-        <v>132.2</v>
+        <v>243.52</v>
       </c>
       <c r="E29" t="n">
-        <v>6.6</v>
+        <v>-0.5</v>
       </c>
       <c r="F29" t="n">
-        <v>67.83</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>1.98</v>
+        <v>1.11</v>
       </c>
       <c r="H29" t="n">
         <v>3</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CHEMBONDCH</t>
+          <t>AFFORDABLE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CHEMBOND CHEMICALS LIMITED</t>
+          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>242.4</v>
+        <v>170.74</v>
       </c>
       <c r="D30" t="n">
-        <v>243.52</v>
+        <v>174.27</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.5</v>
+        <v>-2</v>
       </c>
       <c r="F30" t="n">
-        <v>67.65000000000001</v>
+        <v>61.48</v>
       </c>
       <c r="G30" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
     </row>
@@ -14048,7 +14048,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
